--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Omni-SR/OmniSR+50T+50EP+optim_purn/params_vs_psnr_analysis/OmniSR_hutcn_hyperopt_study_full.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/Omni-SR/OmniSR+50T+50EP+optim_purn/params_vs_psnr_analysis/OmniSR_hutcn_hyperopt_study_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,50 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>flops_G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hp_n_feats</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp_num_heads</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hp_num_blocks</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hp_window_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hp_patch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hp_optimizer</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hp_scheduler</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hp_loss</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hp_lr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hp_weight_decay</t>
         </is>
@@ -506,39 +511,42 @@
         <v>29.00486679077148</v>
       </c>
       <c r="D2" t="n">
+        <v>0.999764172</v>
+      </c>
+      <c r="E2" t="n">
         <v>88</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>12</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>192</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>4.192159350410976e-05</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2.334586407601622e-05</v>
       </c>
     </row>
@@ -553,39 +561,42 @@
         <v>28.11308135986328</v>
       </c>
       <c r="D3" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="E3" t="n">
         <v>120</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>8</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>16</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>128</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>8.488762161408708e-05</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3.585612610345399e-06</v>
       </c>
     </row>
@@ -600,39 +611,42 @@
         <v>30.60256423950195</v>
       </c>
       <c r="D4" t="n">
+        <v>3.304958976</v>
+      </c>
+      <c r="E4" t="n">
         <v>128</v>
       </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>224</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.0002429095036825497</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.0001319994226153501</v>
       </c>
     </row>
@@ -647,39 +661,42 @@
         <v>27.89981384277344</v>
       </c>
       <c r="D5" t="n">
+        <v>2.419237296</v>
+      </c>
+      <c r="E5" t="n">
         <v>112</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
         <v>8</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>256</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1.104552426030472e-05</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>2.107047280657824e-06</v>
       </c>
     </row>
@@ -694,39 +711,42 @@
         <v>27.10241432189941</v>
       </c>
       <c r="D6" t="n">
+        <v>0.5591232</v>
+      </c>
+      <c r="E6" t="n">
         <v>64</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>16</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>12</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>224</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1.538065811598201e-05</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>4.828424974818325e-06</v>
       </c>
     </row>
@@ -741,39 +761,42 @@
         <v>27.84151496887207</v>
       </c>
       <c r="D7" t="n">
+        <v>1.313421516</v>
+      </c>
+      <c r="E7" t="n">
         <v>88</v>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
       <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>16</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>128</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>1.223096868463762e-05</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6.85392570885306e-06</v>
       </c>
     </row>
@@ -788,39 +811,42 @@
         <v>29.17798461914062</v>
       </c>
       <c r="D8" t="n">
+        <v>2.014129152</v>
+      </c>
+      <c r="E8" t="n">
         <v>128</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>128</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>2.425546071605744e-05</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>8.620220426018051e-05</v>
       </c>
     </row>
@@ -835,39 +861,42 @@
         <v>24.90312538146973</v>
       </c>
       <c r="D9" t="n">
+        <v>0.850428396</v>
+      </c>
+      <c r="E9" t="n">
         <v>72</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>12</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>192</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.0003214646526467849</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.0002185881616232416</v>
       </c>
     </row>
@@ -882,39 +911,42 @@
         <v>28.00323028564453</v>
       </c>
       <c r="D10" t="n">
+        <v>1.36351566</v>
+      </c>
+      <c r="E10" t="n">
         <v>104</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>12</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>192</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>4.214422962057283e-05</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>6.24607368131809e-06</v>
       </c>
     </row>
@@ -929,39 +961,42 @@
         <v>30.38225173950195</v>
       </c>
       <c r="D11" t="n">
+        <v>1.4067756</v>
+      </c>
+      <c r="E11" t="n">
         <v>80</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
       <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>160</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.0004336720537130751</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.0003622666594728666</v>
       </c>
     </row>
@@ -976,39 +1011,42 @@
         <v>30.51455879211426</v>
       </c>
       <c r="D12" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="E12" t="n">
         <v>128</v>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
       <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>224</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.0001841435585451208</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.00094861065051841</v>
       </c>
     </row>
@@ -1023,39 +1061,42 @@
         <v>30.49529228210449</v>
       </c>
       <c r="D13" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="E13" t="n">
         <v>128</v>
       </c>
-      <c r="E13" t="n">
-        <v>4</v>
-      </c>
       <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>8</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>224</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.0001842575812298374</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.0008053792205311838</v>
       </c>
     </row>
@@ -1070,39 +1111,42 @@
         <v>30.45342979431152</v>
       </c>
       <c r="D14" t="n">
+        <v>2.419237296</v>
+      </c>
+      <c r="E14" t="n">
         <v>112</v>
       </c>
-      <c r="E14" t="n">
-        <v>4</v>
-      </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>224</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.0001664762121627306</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>7.857007902672141e-05</v>
       </c>
     </row>
@@ -1117,39 +1161,42 @@
         <v>30.54413642883301</v>
       </c>
       <c r="D15" t="n">
+        <v>2.733124608</v>
+      </c>
+      <c r="E15" t="n">
         <v>128</v>
       </c>
-      <c r="E15" t="n">
-        <v>4</v>
-      </c>
       <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>224</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.0001992888514425605</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.0009728613904848122</v>
       </c>
     </row>
@@ -1164,39 +1211,42 @@
         <v>30.69737014770508</v>
       </c>
       <c r="D16" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="E16" t="n">
         <v>120</v>
       </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
       <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>16</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>256</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>0.0002768010920909096</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>2.322775435311717e-05</v>
       </c>
     </row>
@@ -1211,39 +1261,42 @@
         <v>30.71955413818359</v>
       </c>
       <c r="D17" t="n">
+        <v>2.02132728</v>
+      </c>
+      <c r="E17" t="n">
         <v>112</v>
       </c>
-      <c r="E17" t="n">
-        <v>4</v>
-      </c>
       <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>16</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>256</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.0004970004815657692</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2.176686985259424e-05</v>
       </c>
     </row>
@@ -1258,39 +1311,42 @@
         <v>30.60545120239258</v>
       </c>
       <c r="D18" t="n">
+        <v>2.02132728</v>
+      </c>
+      <c r="E18" t="n">
         <v>112</v>
       </c>
-      <c r="E18" t="n">
-        <v>4</v>
-      </c>
       <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>16</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>256</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.0004766419450243131</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2.088479835345855e-05</v>
       </c>
     </row>
@@ -1305,39 +1361,42 @@
         <v>30.61178092956543</v>
       </c>
       <c r="D19" t="n">
+        <v>1.768706316</v>
+      </c>
+      <c r="E19" t="n">
         <v>104</v>
       </c>
-      <c r="E19" t="n">
-        <v>4</v>
-      </c>
       <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>16</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>256</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.0003143787632987575</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1.395090320563265e-05</v>
       </c>
     </row>
@@ -1352,39 +1411,42 @@
         <v>30.57768096923828</v>
       </c>
       <c r="D20" t="n">
+        <v>1.768706316</v>
+      </c>
+      <c r="E20" t="n">
         <v>104</v>
       </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
       <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>16</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>256</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.0003245859176939388</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>1.185895064334954e-05</v>
       </c>
     </row>
@@ -1399,39 +1461,42 @@
         <v>30.72742881774902</v>
       </c>
       <c r="D21" t="n">
+        <v>2.29060062</v>
+      </c>
+      <c r="E21" t="n">
         <v>120</v>
       </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
       <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>16</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>256</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.0004040250792903794</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1.275529370776767e-05</v>
       </c>
     </row>
@@ -1446,39 +1511,42 @@
         <v>30.66411781311035</v>
       </c>
       <c r="D22" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="E22" t="n">
         <v>120</v>
       </c>
-      <c r="E22" t="n">
-        <v>4</v>
-      </c>
       <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>16</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>160</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.0004382126581194218</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>4.704927707037195e-05</v>
       </c>
     </row>
@@ -1493,39 +1561,42 @@
         <v>30.57785339355469</v>
       </c>
       <c r="D23" t="n">
+        <v>2.29060062</v>
+      </c>
+      <c r="E23" t="n">
         <v>120</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>16</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>256</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.0002352113234417836</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>9.106118871391806e-06</v>
       </c>
     </row>
@@ -1540,39 +1611,42 @@
         <v>30.60219688415527</v>
       </c>
       <c r="D24" t="n">
+        <v>2.7360099</v>
+      </c>
+      <c r="E24" t="n">
         <v>120</v>
       </c>
-      <c r="E24" t="n">
-        <v>4</v>
-      </c>
       <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>16</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>160</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>0.0002600834233642106</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>6.564533068411364e-05</v>
       </c>
     </row>
@@ -1587,39 +1661,42 @@
         <v>30.57052917480469</v>
       </c>
       <c r="D25" t="n">
+        <v>2.418463152</v>
+      </c>
+      <c r="E25" t="n">
         <v>112</v>
       </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
       <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>16</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>160</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>0.0004365134206427155</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>2.17096570194637e-05</v>
       </c>
     </row>
@@ -1634,39 +1711,42 @@
         <v>30.56224212646485</v>
       </c>
       <c r="D26" t="n">
+        <v>1.313421516</v>
+      </c>
+      <c r="E26" t="n">
         <v>88</v>
       </c>
-      <c r="E26" t="n">
-        <v>4</v>
-      </c>
       <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>16</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>256</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>0.0004766094122816374</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>3.586711065659111e-06</v>
       </c>
     </row>
@@ -1681,39 +1761,42 @@
         <v>30.77863502502441</v>
       </c>
       <c r="D27" t="n">
+        <v>3.072863232</v>
+      </c>
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="E27" t="n">
-        <v>4</v>
-      </c>
       <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>16</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>256</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>0.000414082661423836</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>9.433622855066785e-06</v>
       </c>
     </row>
